--- a/output/北塩原村_アンケート報告書_構成案.xlsx
+++ b/output/北塩原村_アンケート報告書_構成案.xlsx
@@ -2512,7 +2512,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>見込量 第5章4（村確認事項M-4）</t>
+          <t>見込量 第5章4（村確認事項Ｍ-4）</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>他サービスとの混同か、村外事業所の利用か。見込量の置き方が変わる（M-4・M-13）</t>
+          <t>他サービスとの混同か、村外事業所の利用か。見込量の置き方が変わる（Ｍ-4・Ｍ-13）</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>開始直後の利用か回答の誤りかを確認する（M-13）</t>
+          <t>開始直後の利用か回答の誤りかを確認する（Ｍ-13）</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>就学による移行であれば整合する。急減の理由を確認する（M-1）</t>
+          <t>就学による移行であれば整合する。急減の理由を確認する（Ｍ-1）</t>
         </is>
       </c>
     </row>
